--- a/Program/CAISO-API/Month_Agg/CAISO_NG_2024_06.xlsx
+++ b/Program/CAISO-API/Month_Agg/CAISO_NG_2024_06.xlsx
@@ -1603,20 +1603,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="SimSun"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1664,7 +1664,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1727,8 +1727,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1761,8 +1761,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
